--- a/FY Separation Summary.xlsx
+++ b/FY Separation Summary.xlsx
@@ -6280,9 +6280,15 @@
       <c r="N49" s="6"/>
     </row>
     <row r="50" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="6"/>
+      <c r="A50" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling 12-month Turnover:</t>
+        </is>
+      </c>
       <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
+      <c r="C50" s="34">
+        <f>IFERROR((SUMPRODUCT((ISNUMBER('FY 2023 (Jan23-Dec23)'!$B$9:$B$412))*(('FY 2023 (Jan23-Dec23)'!$B$9:$B$412&gt;=TODAY()-365)*('FY 2023 (Jan23-Dec23)'!$B$9:$B$412&lt;=TODAY())))+SUMPRODUCT((ISNUMBER('FY 2024 (Jan24-Dec24)'!$B$9:$B$412))*(('FY 2024 (Jan24-Dec24)'!$B$9:$B$412&gt;=TODAY()-365)*('FY 2024 (Jan24-Dec24)'!$B$9:$B$412&lt;=TODAY())))+SUMPRODUCT((ISNUMBER('FY 2025 (Jan25-Dec25)'!$B$9:$B$412))*(('FY 2025 (Jan25-Dec25)'!$B$9:$B$412&gt;=TODAY()-365)*('FY 2025 (Jan25-Dec25)'!$B$9:$B$412&lt;=TODAY())))+SUMPRODUCT((ISNUMBER('FY 2026 (Jan26-Dec26)'!$B$9:$B$412))*(('FY 2026 (Jan26-Dec26)'!$B$9:$B$412&gt;=TODAY()-365)*('FY 2026 (Jan26-Dec26)'!$B$9:$B$412&lt;=TODAY())))+SUMPRODUCT((ISNUMBER('FY 2027 (Jan27-Dec27)'!$B$9:$B$412))*(('FY 2027 (Jan27-Dec27)'!$B$9:$B$412&gt;=TODAY()-365)*('FY 2027 (Jan27-Dec27)'!$B$9:$B$412&lt;=TODAY()))))/VLOOKUP($B$5,Data!$A$2:$K$6,2,FALSE),0)</f>
+      </c>
       <c r="D50" s="6"/>
       <c r="E50" s="6"/>
       <c r="F50" s="13"/>
@@ -6298,9 +6304,15 @@
       <c r="N50" s="6"/>
     </row>
     <row r="51" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="6"/>
+      <c r="A51" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avg Tenure at Separation:</t>
+        </is>
+      </c>
       <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
+      <c r="C51" s="34">
+        <f>IFERROR(IF(SUMPRODUCT((INDIRECT("'"&amp;$B$5&amp;" (Jan"&amp;RIGHT($B$5,2)&amp;"-Dec"&amp;RIGHT($B$5,2)&amp;")'!B9:B412")&lt;&gt;"")*(INDIRECT("'"&amp;$B$5&amp;" (Jan"&amp;RIGHT($B$5,2)&amp;"-Dec"&amp;RIGHT($B$5,2)&amp;")'!C9:C412")&lt;&gt;""))=0,"N/A (no DOH data)",(SUMPRODUCT((INDIRECT("'"&amp;$B$5&amp;" (Jan"&amp;RIGHT($B$5,2)&amp;"-Dec"&amp;RIGHT($B$5,2)&amp;")'!B9:B412")&lt;&gt;"")*(INDIRECT("'"&amp;$B$5&amp;" (Jan"&amp;RIGHT($B$5,2)&amp;"-Dec"&amp;RIGHT($B$5,2)&amp;")'!C9:C412")&lt;&gt;"")*(INDIRECT("'"&amp;$B$5&amp;" (Jan"&amp;RIGHT($B$5,2)&amp;"-Dec"&amp;RIGHT($B$5,2)&amp;")'!B9:B412")-INDIRECT("'"&amp;$B$5&amp;" (Jan"&amp;RIGHT($B$5,2)&amp;"-Dec"&amp;RIGHT($B$5,2)&amp;")'!C9:C412"))))/SUMPRODUCT((INDIRECT("'"&amp;$B$5&amp;" (Jan"&amp;RIGHT($B$5,2)&amp;"-Dec"&amp;RIGHT($B$5,2)&amp;")'!B9:B412")&lt;&gt;"")*(INDIRECT("'"&amp;$B$5&amp;" (Jan"&amp;RIGHT($B$5,2)&amp;"-Dec"&amp;RIGHT($B$5,2)&amp;")'!C9:C412")&lt;&gt;""))/365.25),"N/A (no DOH data)")</f>
+      </c>
       <c r="D51" s="6"/>
       <c r="E51" s="6"/>
       <c r="F51" s="13"/>
@@ -18867,12 +18879,6 @@
     <mergeCell ref="A211:M211"/>
     <mergeCell ref="A245:M245"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Entry" error="Please select a value from the list." sqref="E9:E413" xr:uid="{00000000-0002-0000-0200-000005000000}">
-      <formula1>"Yes,No"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <extLst>
@@ -18925,6 +18931,46 @@
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4B89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Rehire" error="Rehire Eligibility must be Yes or No." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0005-00000000}">
+          <x14:formula1>
+            <xm:f>Reference!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E9:E413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Status" error="Status must be U (uneligible) or D (discharged)." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0005-00000001}">
+          <x14:formula1>
+            <xm:f>Reference!$G$2:$G$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>F9:F413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Location" error="Pick a location from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0005-00000002}">
+          <x14:formula1>
+            <xm:f>Reference!$E$2:$E$64</xm:f>
+          </x14:formula1>
+          <xm:sqref>G9:G413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Reason" error="Pick a reason from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0005-00000003}">
+          <x14:formula1>
+            <xm:f>Reference!$C$2:$C$14</xm:f>
+          </x14:formula1>
+          <xm:sqref>H9:H413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Job" error="Pick a job from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0005-00000004}">
+          <x14:formula1>
+            <xm:f>Reference!$A$2:$A$18</xm:f>
+          </x14:formula1>
+          <xm:sqref>K9:K413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Department" error="Pick a department from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0005-00000005}">
+          <x14:formula1>
+            <xm:f>Reference!$L$2:$L$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>M9:M413</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
   </extLst>
 </worksheet>
 </file>
@@ -20700,7 +20746,7 @@
         <v>163</v>
       </c>
       <c r="B51" s="107">
-        <v>10</v>
+        <f>COUNTA(A37:A47)</f>
       </c>
       <c r="C51" s="108"/>
       <c r="D51" s="108"/>
@@ -27126,12 +27172,6 @@
     <mergeCell ref="A155:M155"/>
     <mergeCell ref="A189:M189"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Entry" error="Please select a value from the list." sqref="E9:E357" xr:uid="{00000000-0002-0000-0300-000005000000}">
-      <formula1>"Yes,No"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
@@ -27187,6 +27227,46 @@
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4B89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Rehire" error="Rehire Eligibility must be Yes or No." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0004-00000000}">
+          <x14:formula1>
+            <xm:f>Reference!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E9:E357</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Status" error="Status must be U (uneligible) or D (discharged)." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0004-00000001}">
+          <x14:formula1>
+            <xm:f>Reference!$G$2:$G$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>F9:F357</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Location" error="Pick a location from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0004-00000002}">
+          <x14:formula1>
+            <xm:f>Reference!$E$2:$E$64</xm:f>
+          </x14:formula1>
+          <xm:sqref>G9:G357</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Reason" error="Pick a reason from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0004-00000003}">
+          <x14:formula1>
+            <xm:f>Reference!$C$2:$C$14</xm:f>
+          </x14:formula1>
+          <xm:sqref>H9:H357</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Job" error="Pick a job from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0004-00000004}">
+          <x14:formula1>
+            <xm:f>Reference!$A$2:$A$18</xm:f>
+          </x14:formula1>
+          <xm:sqref>K9:K357</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Department" error="Pick a department from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0004-00000005}">
+          <x14:formula1>
+            <xm:f>Reference!$L$2:$L$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>M9:M357</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
   </extLst>
 </worksheet>
 </file>
@@ -37738,12 +37818,6 @@
     <mergeCell ref="A211:M211"/>
     <mergeCell ref="A245:M245"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Entry" error="Please select a value from the list." sqref="E9:E413" xr:uid="{00000000-0002-0000-0400-000005000000}">
-      <formula1>"Yes,No"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <extLst>
@@ -37796,6 +37870,46 @@
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4B89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Rehire" error="Rehire Eligibility must be Yes or No." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0003-00000000}">
+          <x14:formula1>
+            <xm:f>Reference!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E9:E413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Status" error="Status must be U (uneligible) or D (discharged)." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0003-00000001}">
+          <x14:formula1>
+            <xm:f>Reference!$G$2:$G$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>F9:F413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Location" error="Pick a location from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0003-00000002}">
+          <x14:formula1>
+            <xm:f>Reference!$E$2:$E$64</xm:f>
+          </x14:formula1>
+          <xm:sqref>G9:G413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Reason" error="Pick a reason from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0003-00000003}">
+          <x14:formula1>
+            <xm:f>Reference!$C$2:$C$14</xm:f>
+          </x14:formula1>
+          <xm:sqref>H9:H413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Job" error="Pick a job from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0003-00000004}">
+          <x14:formula1>
+            <xm:f>Reference!$A$2:$A$18</xm:f>
+          </x14:formula1>
+          <xm:sqref>K9:K413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Department" error="Pick a department from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0003-00000005}">
+          <x14:formula1>
+            <xm:f>Reference!$L$2:$L$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>M9:M413</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
   </extLst>
 </worksheet>
 </file>
@@ -48314,12 +48428,6 @@
     <mergeCell ref="A211:M211"/>
     <mergeCell ref="A245:M245"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Entry" error="Please select a value from the list." sqref="E9:E413" xr:uid="{00000000-0002-0000-0500-000005000000}">
-      <formula1>"Yes,No"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <extLst>
@@ -48372,6 +48480,46 @@
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4B89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Rehire" error="Rehire Eligibility must be Yes or No." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0002-00000000}">
+          <x14:formula1>
+            <xm:f>Reference!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E9:E413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Status" error="Status must be U (uneligible) or D (discharged)." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0002-00000001}">
+          <x14:formula1>
+            <xm:f>Reference!$G$2:$G$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>F9:F413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Location" error="Pick a location from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0002-00000002}">
+          <x14:formula1>
+            <xm:f>Reference!$E$2:$E$64</xm:f>
+          </x14:formula1>
+          <xm:sqref>G9:G413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Reason" error="Pick a reason from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0002-00000003}">
+          <x14:formula1>
+            <xm:f>Reference!$C$2:$C$14</xm:f>
+          </x14:formula1>
+          <xm:sqref>H9:H413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Job" error="Pick a job from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0002-00000004}">
+          <x14:formula1>
+            <xm:f>Reference!$A$2:$A$18</xm:f>
+          </x14:formula1>
+          <xm:sqref>K9:K413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Department" error="Pick a department from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0002-00000005}">
+          <x14:formula1>
+            <xm:f>Reference!$L$2:$L$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>M9:M413</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
   </extLst>
 </worksheet>
 </file>
@@ -57096,12 +57244,6 @@
     <mergeCell ref="A211:M211"/>
     <mergeCell ref="A245:M245"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid Entry" error="Please select a value from the list." sqref="E9:E413" xr:uid="{00000000-0002-0000-0600-000005000000}">
-      <formula1>"Yes,No"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <extLst>
@@ -57154,6 +57296,46 @@
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4B89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Rehire" error="Rehire Eligibility must be Yes or No." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0001-00000000}">
+          <x14:formula1>
+            <xm:f>Reference!$B$2:$B$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E9:E413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Status" error="Status must be U (uneligible) or D (discharged)." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0001-00000001}">
+          <x14:formula1>
+            <xm:f>Reference!$G$2:$G$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>F9:F413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Location" error="Pick a location from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0001-00000002}">
+          <x14:formula1>
+            <xm:f>Reference!$E$2:$E$64</xm:f>
+          </x14:formula1>
+          <xm:sqref>G9:G413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Reason" error="Pick a reason from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0001-00000003}">
+          <x14:formula1>
+            <xm:f>Reference!$C$2:$C$14</xm:f>
+          </x14:formula1>
+          <xm:sqref>H9:H413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Job" error="Pick a job from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0001-00000004}">
+          <x14:formula1>
+            <xm:f>Reference!$A$2:$A$18</xm:f>
+          </x14:formula1>
+          <xm:sqref>K9:K413</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" type="list" errorStyle="stop" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid Department" error="Pick a department from the Reference list." promptTitle="" prompt="" xr:uid="{00000000-0002-0000-0001-00000005}">
+          <x14:formula1>
+            <xm:f>Reference!$L$2:$L$10</xm:f>
+          </x14:formula1>
+          <xm:sqref>M9:M413</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
   </extLst>
 </worksheet>
 </file>
@@ -57213,8 +57395,7 @@
         <v>103</v>
       </c>
       <c r="B2" s="6">
-        <f>'FY 2023 (Jan23-Dec23)'!B5</f>
-        <v>339</v>
+        <f>IFERROR(VLOOKUP("FY 2023",Reference!$N$2:$O$6,2,FALSE),0)</f>
       </c>
       <c r="C2" s="6">
         <f>'FY 2023 (Jan23-Dec23)'!E5</f>
@@ -57225,20 +57406,16 @@
         <v>0.18289085545722714</v>
       </c>
       <c r="E2" s="6">
-        <f>IFERROR(C2/COUNTIF(B11:M11,"&gt;0"),0)</f>
-        <v>10.333333333333334</v>
+        <f>IFERROR(C2/IF(VALUE(RIGHT(A2,4))&lt;YEAR(TODAY()),12,IF(VALUE(RIGHT(A2,4))&gt;YEAR(TODAY()),NA(),MONTH(TODAY()))),0)</f>
       </c>
       <c r="F2" s="6">
-        <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Resignation")+COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Better Opportunity")+COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Personal Reasons")+COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Relocation")+COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Retirement")</f>
-        <v>36</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Voluntary")*Data!$C$56:$C$68)</f>
       </c>
       <c r="G2" s="6">
-        <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Termination")+COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Layoff")</f>
-        <v>4</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Involuntary")*Data!$C$56:$C$68)</f>
       </c>
       <c r="H2" s="6">
-        <f>C2-F2-G2</f>
-        <v>22</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Other")*Data!$C$56:$C$68)</f>
       </c>
       <c r="I2" s="6">
         <f>IF(C2=0,0,F2/C2)</f>
@@ -57264,8 +57441,7 @@
         <v>104</v>
       </c>
       <c r="B3" s="6">
-        <f>'FY 2024 (Jan24-Dec24)'!B5</f>
-        <v>339</v>
+        <f>IFERROR(VLOOKUP("FY 2024",Reference!$N$2:$O$6,2,FALSE),0)</f>
       </c>
       <c r="C3" s="6">
         <f>'FY 2024 (Jan24-Dec24)'!E5</f>
@@ -57276,20 +57452,16 @@
         <v>0.46607669616519176</v>
       </c>
       <c r="E3" s="6">
-        <f>IFERROR(C3/COUNTIF(B12:M12,"&gt;0"),0)</f>
-        <v>13.166666666666666</v>
+        <f>IFERROR(C3/IF(VALUE(RIGHT(A3,4))&lt;YEAR(TODAY()),12,IF(VALUE(RIGHT(A3,4))&gt;YEAR(TODAY()),NA(),MONTH(TODAY()))),0)</f>
       </c>
       <c r="F3" s="6">
-        <f>COUNTIF('FY 2024 (Jan24-Dec24)'!H9:H412,"Resignation")+COUNTIF('FY 2024 (Jan24-Dec24)'!H9:H412,"Better Opportunity")+COUNTIF('FY 2024 (Jan24-Dec24)'!H9:H412,"Personal Reasons")+COUNTIF('FY 2024 (Jan24-Dec24)'!H9:H412,"Relocation")+COUNTIF('FY 2024 (Jan24-Dec24)'!H9:H412,"Retirement")</f>
-        <v>87</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Voluntary")*Data!$D$56:$D$68)</f>
       </c>
       <c r="G3" s="6">
-        <f>COUNTIF('FY 2024 (Jan24-Dec24)'!H9:H412,"Termination")+COUNTIF('FY 2024 (Jan24-Dec24)'!H9:H412,"Layoff")</f>
-        <v>13</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Involuntary")*Data!$D$56:$D$68)</f>
       </c>
       <c r="H3" s="6">
-        <f>C3-F3-G3</f>
-        <v>58</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Other")*Data!$D$56:$D$68)</f>
       </c>
       <c r="I3" s="6">
         <f>IF(C3=0,0,F3/C3)</f>
@@ -57315,8 +57487,7 @@
         <v>105</v>
       </c>
       <c r="B4" s="6">
-        <f>'FY 2025 (Jan25-Dec25)'!B5</f>
-        <v>346</v>
+        <f>IFERROR(VLOOKUP("FY 2025",Reference!$N$2:$O$6,2,FALSE),0)</f>
       </c>
       <c r="C4" s="6">
         <f>'FY 2025 (Jan25-Dec25)'!E5</f>
@@ -57327,20 +57498,16 @@
         <v>0.39884393063583817</v>
       </c>
       <c r="E4" s="6">
-        <f>IFERROR(C4/COUNTIF(B13:M13,"&gt;0"),0)</f>
-        <v>11.5</v>
+        <f>IFERROR(C4/IF(VALUE(RIGHT(A4,4))&lt;YEAR(TODAY()),12,IF(VALUE(RIGHT(A4,4))&gt;YEAR(TODAY()),NA(),MONTH(TODAY()))),0)</f>
       </c>
       <c r="F4" s="6">
-        <f>COUNTIF('FY 2025 (Jan25-Dec25)'!H9:H412,"Resignation")+COUNTIF('FY 2025 (Jan25-Dec25)'!H9:H412,"Better Opportunity")+COUNTIF('FY 2025 (Jan25-Dec25)'!H9:H412,"Personal Reasons")+COUNTIF('FY 2025 (Jan25-Dec25)'!H9:H412,"Relocation")+COUNTIF('FY 2025 (Jan25-Dec25)'!H9:H412,"Retirement")</f>
-        <v>98</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Voluntary")*Data!$E$56:$E$68)</f>
       </c>
       <c r="G4" s="6">
-        <f>COUNTIF('FY 2025 (Jan25-Dec25)'!H9:H412,"Termination")+COUNTIF('FY 2025 (Jan25-Dec25)'!H9:H412,"Layoff")</f>
-        <v>5</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Involuntary")*Data!$E$56:$E$68)</f>
       </c>
       <c r="H4" s="6">
-        <f>C4-F4-G4</f>
-        <v>35</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Other")*Data!$E$56:$E$68)</f>
       </c>
       <c r="I4" s="6">
         <f>IF(C4=0,0,F4/C4)</f>
@@ -57366,8 +57533,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="6">
-        <f>'FY 2026 (Jan26-Dec26)'!B5</f>
-        <v>366</v>
+        <f>IFERROR(VLOOKUP("FY 2026",Reference!$N$2:$O$6,2,FALSE),0)</f>
       </c>
       <c r="C5" s="6">
         <f>'FY 2026 (Jan26-Dec26)'!E5</f>
@@ -57378,20 +57544,16 @@
         <v>9.5628415300546443E-2</v>
       </c>
       <c r="E5" s="6">
-        <f>IFERROR(C5/COUNTIF(B14:M14,"&gt;0"),0)</f>
-        <v>8.75</v>
+        <f>IFERROR(C5/IF(VALUE(RIGHT(A5,4))&lt;YEAR(TODAY()),12,IF(VALUE(RIGHT(A5,4))&gt;YEAR(TODAY()),NA(),MONTH(TODAY()))),0)</f>
       </c>
       <c r="F5" s="6">
-        <f>COUNTIF('FY 2026 (Jan26-Dec26)'!H9:H356,"Resignation")+COUNTIF('FY 2026 (Jan26-Dec26)'!H9:H356,"Better Opportunity")+COUNTIF('FY 2026 (Jan26-Dec26)'!H9:H356,"Personal Reasons")+COUNTIF('FY 2026 (Jan26-Dec26)'!H9:H356,"Relocation")+COUNTIF('FY 2026 (Jan26-Dec26)'!H9:H356,"Retirement")</f>
-        <v>21</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Voluntary")*Data!$F$56:$F$68)</f>
       </c>
       <c r="G5" s="6">
-        <f>COUNTIF('FY 2026 (Jan26-Dec26)'!H9:H356,"Termination")+COUNTIF('FY 2026 (Jan26-Dec26)'!H9:H356,"Layoff")</f>
-        <v>4</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Involuntary")*Data!$F$56:$F$68)</f>
       </c>
       <c r="H5" s="6">
-        <f>C5-F5-G5</f>
-        <v>10</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Other")*Data!$F$56:$F$68)</f>
       </c>
       <c r="I5" s="6">
         <f>IF(C5=0,0,F5/C5)</f>
@@ -57417,8 +57579,7 @@
         <v>106</v>
       </c>
       <c r="B6" s="6">
-        <f>'FY 2027 (Jan27-Dec27)'!B5</f>
-        <v>364</v>
+        <f>IFERROR(VLOOKUP("FY 2027",Reference!$N$2:$O$6,2,FALSE),0)</f>
       </c>
       <c r="C6" s="6">
         <f>'FY 2027 (Jan27-Dec27)'!E5</f>
@@ -57429,20 +57590,16 @@
         <v>0</v>
       </c>
       <c r="E6" s="6">
-        <f>IFERROR(C6/COUNTIF(B15:M15,"&gt;0"),0)</f>
-        <v>0</v>
+        <f>IFERROR(C6/IF(VALUE(RIGHT(A6,4))&lt;YEAR(TODAY()),12,IF(VALUE(RIGHT(A6,4))&gt;YEAR(TODAY()),NA(),MONTH(TODAY()))),0)</f>
       </c>
       <c r="F6" s="6">
-        <f>COUNTIF('FY 2027 (Jan27-Dec27)'!H9:H412,"Resignation")+COUNTIF('FY 2027 (Jan27-Dec27)'!H9:H412,"Better Opportunity")+COUNTIF('FY 2027 (Jan27-Dec27)'!H9:H412,"Personal Reasons")+COUNTIF('FY 2027 (Jan27-Dec27)'!H9:H412,"Relocation")+COUNTIF('FY 2027 (Jan27-Dec27)'!H9:H412,"Retirement")</f>
-        <v>0</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Voluntary")*Data!$G$56:$G$68)</f>
       </c>
       <c r="G6" s="6">
-        <f>COUNTIF('FY 2027 (Jan27-Dec27)'!H9:H412,"Termination")+COUNTIF('FY 2027 (Jan27-Dec27)'!H9:H412,"Layoff")</f>
-        <v>0</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Involuntary")*Data!$G$56:$G$68)</f>
       </c>
       <c r="H6" s="6">
-        <f>C6-F6-G6</f>
-        <v>0</v>
+        <f>SUMPRODUCT((Data!$B$56:$B$68="Other")*Data!$G$56:$G$68)</f>
       </c>
       <c r="I6" s="6">
         <f>IF(C6=0,0,F6/C6)</f>
@@ -59086,8 +59243,8 @@
       <c r="A56" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B56" s="6" t="s">
-        <v>54</v>
+      <c r="B56" s="6">
+        <f>IFERROR(VLOOKUP(A56,Reference!$C$2:$D$14,2,FALSE),"Other")</f>
       </c>
       <c r="C56" s="6">
         <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Resignation")</f>
@@ -59122,8 +59279,8 @@
       <c r="A57" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B57" s="6" t="s">
-        <v>54</v>
+      <c r="B57" s="6">
+        <f>IFERROR(VLOOKUP(A57,Reference!$C$2:$D$14,2,FALSE),"Other")</f>
       </c>
       <c r="C57" s="6">
         <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Better Opportunity")</f>
@@ -59158,8 +59315,8 @@
       <c r="A58" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>54</v>
+      <c r="B58" s="6">
+        <f>IFERROR(VLOOKUP(A58,Reference!$C$2:$D$14,2,FALSE),"Other")</f>
       </c>
       <c r="C58" s="6">
         <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Personal Reasons")</f>
@@ -59194,8 +59351,8 @@
       <c r="A59" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B59" s="6" t="s">
-        <v>54</v>
+      <c r="B59" s="6">
+        <f>IFERROR(VLOOKUP(A59,Reference!$C$2:$D$14,2,FALSE),"Other")</f>
       </c>
       <c r="C59" s="6">
         <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Relocation")</f>
@@ -59230,8 +59387,8 @@
       <c r="A60" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>54</v>
+      <c r="B60" s="6">
+        <f>IFERROR(VLOOKUP(A60,Reference!$C$2:$D$14,2,FALSE),"Other")</f>
       </c>
       <c r="C60" s="6">
         <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Retirement")</f>
@@ -59266,8 +59423,8 @@
       <c r="A61" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B61" s="6" t="s">
-        <v>65</v>
+      <c r="B61" s="6">
+        <f>IFERROR(VLOOKUP(A61,Reference!$C$2:$D$14,2,FALSE),"Other")</f>
       </c>
       <c r="C61" s="6">
         <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Termination")</f>
@@ -59302,8 +59459,8 @@
       <c r="A62" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B62" s="6" t="s">
-        <v>65</v>
+      <c r="B62" s="6">
+        <f>IFERROR(VLOOKUP(A62,Reference!$C$2:$D$14,2,FALSE),"Other")</f>
       </c>
       <c r="C62" s="6">
         <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Layoff")</f>
@@ -59338,8 +59495,8 @@
       <c r="A63" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B63" s="6" t="s">
-        <v>70</v>
+      <c r="B63" s="6">
+        <f>IFERROR(VLOOKUP(A63,Reference!$C$2:$D$14,2,FALSE),"Other")</f>
       </c>
       <c r="C63" s="6">
         <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Job Abandonment")</f>
@@ -59374,8 +59531,8 @@
       <c r="A64" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B64" s="6" t="s">
-        <v>70</v>
+      <c r="B64" s="6">
+        <f>IFERROR(VLOOKUP(A64,Reference!$C$2:$D$14,2,FALSE),"Other")</f>
       </c>
       <c r="C64" s="6">
         <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"End of Contract")</f>
@@ -59410,8 +59567,8 @@
       <c r="A65" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="B65" s="6" t="s">
-        <v>70</v>
+      <c r="B65" s="6">
+        <f>IFERROR(VLOOKUP(A65,Reference!$C$2:$D$14,2,FALSE),"Other")</f>
       </c>
       <c r="C65" s="6">
         <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Other")</f>
@@ -59446,8 +59603,8 @@
       <c r="A66" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B66" s="6" t="s">
-        <v>70</v>
+      <c r="B66" s="6">
+        <f>IFERROR(VLOOKUP(A66,Reference!$C$2:$D$14,2,FALSE),"Other")</f>
       </c>
       <c r="C66" s="6">
         <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Performance Issues")</f>
@@ -59482,8 +59639,8 @@
       <c r="A67" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B67" s="6" t="s">
-        <v>70</v>
+      <c r="B67" s="6">
+        <f>IFERROR(VLOOKUP(A67,Reference!$C$2:$D$14,2,FALSE),"Other")</f>
       </c>
       <c r="C67" s="6">
         <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Attendance Issues")</f>
@@ -59515,13 +59672,29 @@
       <c r="O67" s="6"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
-      <c r="C68" s="6"/>
-      <c r="D68" s="6"/>
-      <c r="E68" s="6"/>
-      <c r="F68" s="6"/>
-      <c r="G68" s="6"/>
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resignation without Notice</t>
+        </is>
+      </c>
+      <c r="B68" s="6">
+        <f>IFERROR(VLOOKUP(A68,Reference!$C$2:$D$14,2,FALSE),"Other")</f>
+      </c>
+      <c r="C68" s="6">
+        <f>COUNTIF('FY 2023 (Jan23-Dec23)'!H9:H412,"Resignation without Notice")</f>
+      </c>
+      <c r="D68" s="6">
+        <f>COUNTIF('FY 2024 (Jan24-Dec24)'!H9:H412,"Resignation without Notice")</f>
+      </c>
+      <c r="E68" s="6">
+        <f>COUNTIF('FY 2025 (Jan25-Dec25)'!H9:H412,"Resignation without Notice")</f>
+      </c>
+      <c r="F68" s="6">
+        <f>COUNTIF('FY 2026 (Jan26-Dec26)'!H9:H412,"Resignation without Notice")</f>
+      </c>
+      <c r="G68" s="6">
+        <f>COUNTIF('FY 2027 (Jan27-Dec27)'!H9:H412,"Resignation without Notice")</f>
+      </c>
       <c r="H68" s="6"/>
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
@@ -62752,11 +62925,19 @@
       <c r="A1" s="145" t="s">
         <v>1007</v>
       </c>
-      <c r="B1" s="6"/>
+      <c r="B1" s="145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rehire Eligibility</t>
+        </is>
+      </c>
       <c r="C1" s="145" t="s">
         <v>1008</v>
       </c>
-      <c r="D1" s="6"/>
+      <c r="D1" s="145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reason Category</t>
+        </is>
+      </c>
       <c r="E1" s="145" t="s">
         <v>1009</v>
       </c>
@@ -62764,7 +62945,11 @@
       <c r="G1" s="145" t="s">
         <v>156</v>
       </c>
-      <c r="H1" s="6"/>
+      <c r="H1" s="145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status Meaning</t>
+        </is>
+      </c>
       <c r="I1" s="145" t="s">
         <v>1010</v>
       </c>
@@ -62775,16 +62960,34 @@
       <c r="L1" s="145" t="s">
         <v>1011</v>
       </c>
+      <c r="N1" t="inlineStr" s="145">
+        <is>
+          <t xml:space="preserve">FY</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr" s="145">
+        <is>
+          <t xml:space="preserve">Active Emp (FY start)</t>
+        </is>
+      </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="80" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="6"/>
+      <c r="B2" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
       <c r="C2" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="6"/>
+      <c r="D2" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Involuntary</t>
+        </is>
+      </c>
       <c r="E2" s="80" t="s">
         <v>248</v>
       </c>
@@ -62792,7 +62995,11 @@
       <c r="G2" s="80" t="s">
         <v>191</v>
       </c>
-      <c r="H2" s="6"/>
+      <c r="H2" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Uneligible for rehire</t>
+        </is>
+      </c>
       <c r="I2" s="80" t="s">
         <v>1012</v>
       </c>
@@ -62803,16 +63010,32 @@
       <c r="L2" s="80" t="s">
         <v>1013</v>
       </c>
+      <c r="N2" t="inlineStr" s="80">
+        <is>
+          <t xml:space="preserve">FY 2023</t>
+        </is>
+      </c>
+      <c r="O2" s="80">
+        <v>339</v>
+      </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="77" t="s">
         <v>226</v>
       </c>
-      <c r="B3" s="6"/>
+      <c r="B3" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No</t>
+        </is>
+      </c>
       <c r="C3" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="6"/>
+      <c r="D3" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voluntary</t>
+        </is>
+      </c>
       <c r="E3" s="77" t="s">
         <v>983</v>
       </c>
@@ -62820,7 +63043,11 @@
       <c r="G3" s="77" t="s">
         <v>180</v>
       </c>
-      <c r="H3" s="6"/>
+      <c r="H3" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Discharged / terminated</t>
+        </is>
+      </c>
       <c r="I3" s="77" t="s">
         <v>259</v>
       </c>
@@ -62831,6 +63058,14 @@
       <c r="L3" s="77" t="s">
         <v>1014</v>
       </c>
+      <c r="N3" t="inlineStr" s="80">
+        <is>
+          <t xml:space="preserve">FY 2024</t>
+        </is>
+      </c>
+      <c r="O3" s="80">
+        <v>339</v>
+      </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="80" t="s">
@@ -62840,7 +63075,11 @@
       <c r="C4" s="80" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other</t>
+        </is>
+      </c>
       <c r="E4" s="80" t="s">
         <v>1015</v>
       </c>
@@ -62857,6 +63096,14 @@
       <c r="L4" s="80" t="s">
         <v>481</v>
       </c>
+      <c r="N4" t="inlineStr" s="80">
+        <is>
+          <t xml:space="preserve">FY 2025</t>
+        </is>
+      </c>
+      <c r="O4" s="80">
+        <v>346</v>
+      </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="77" t="s">
@@ -62866,7 +63113,11 @@
       <c r="C5" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="6"/>
+      <c r="D5" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Involuntary</t>
+        </is>
+      </c>
       <c r="E5" s="77" t="s">
         <v>211</v>
       </c>
@@ -62883,6 +63134,14 @@
       <c r="L5" s="77" t="s">
         <v>259</v>
       </c>
+      <c r="N5" t="inlineStr" s="80">
+        <is>
+          <t xml:space="preserve">FY 2026</t>
+        </is>
+      </c>
+      <c r="O5" s="80">
+        <v>366</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="80" t="s">
@@ -62892,7 +63151,11 @@
       <c r="C6" s="80" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Involuntary</t>
+        </is>
+      </c>
       <c r="E6" s="80" t="s">
         <v>234</v>
       </c>
@@ -62909,6 +63172,14 @@
       <c r="L6" s="80" t="s">
         <v>406</v>
       </c>
+      <c r="N6" t="inlineStr" s="80">
+        <is>
+          <t xml:space="preserve">FY 2027</t>
+        </is>
+      </c>
+      <c r="O6" s="80">
+        <v>364</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="77" t="s">
@@ -62918,7 +63189,11 @@
       <c r="C7" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Other</t>
+        </is>
+      </c>
       <c r="E7" s="77" t="s">
         <v>371</v>
       </c>
@@ -62944,7 +63219,11 @@
       <c r="C8" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Involuntary</t>
+        </is>
+      </c>
       <c r="E8" s="80" t="s">
         <v>1016</v>
       </c>
@@ -62970,7 +63249,11 @@
       <c r="C9" s="77" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="6"/>
+      <c r="D9" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voluntary</t>
+        </is>
+      </c>
       <c r="E9" s="77" t="s">
         <v>1018</v>
       </c>
@@ -62996,7 +63279,11 @@
       <c r="C10" s="80" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="6"/>
+      <c r="D10" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voluntary</t>
+        </is>
+      </c>
       <c r="E10" s="80" t="s">
         <v>208</v>
       </c>
@@ -63022,7 +63309,11 @@
       <c r="C11" s="77" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="6"/>
+      <c r="D11" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voluntary</t>
+        </is>
+      </c>
       <c r="E11" s="77" t="s">
         <v>1019</v>
       </c>
@@ -63046,7 +63337,11 @@
       <c r="C12" s="80" t="s">
         <v>62</v>
       </c>
-      <c r="D12" s="6"/>
+      <c r="D12" s="80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voluntary</t>
+        </is>
+      </c>
       <c r="E12" s="80" t="s">
         <v>1020</v>
       </c>
@@ -63070,7 +63365,11 @@
       <c r="C13" s="77" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="6"/>
+      <c r="D13" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Involuntary</t>
+        </is>
+      </c>
       <c r="E13" s="77" t="s">
         <v>1022</v>
       </c>
@@ -63091,8 +63390,16 @@
         <v>81</v>
       </c>
       <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
+      <c r="C14" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Resignation without Notice</t>
+        </is>
+      </c>
+      <c r="D14" s="77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voluntary</t>
+        </is>
+      </c>
       <c r="E14" s="80" t="s">
         <v>218</v>
       </c>
